--- a/Configs/GameConfig/Datas/giftrandom.xlsx
+++ b/Configs/GameConfig/Datas/giftrandom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,23 @@
         <v>5</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6101</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30101</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
